--- a/template/assets/finance_invoice_template_v1.xlsx
+++ b/template/assets/finance_invoice_template_v1.xlsx
@@ -374,21 +374,9 @@
           <t>备注</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>开票日期</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>销售方</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>购买方</t>
-        </is>
-      </c>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
